--- a/Categoría/UOri_Categoría.xlsx
+++ b/Categoría/UOri_Categoría.xlsx
@@ -833,13 +833,13 @@
         <v>0.4632187993954578</v>
       </c>
       <c r="C2" s="2">
-        <v>112.2262160580291</v>
+        <v>111.2921052077582</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.5198529306309549</v>
+        <v>0.5155259535653073</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2165,7 +2165,7 @@
         <v>6</v>
       </c>
       <c r="E80" s="2">
-        <v>0.3480824918238671</v>
+        <v>0.348082491823867</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2836,10 +2836,10 @@
         <v>124</v>
       </c>
       <c r="B120" s="2">
-        <v>1.735929085329559</v>
+        <v>1.73592908532956</v>
       </c>
       <c r="C120" s="2">
-        <v>112.5569733616862</v>
+        <v>112.5569733616861</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>6</v>
@@ -2904,7 +2904,7 @@
         <v>128</v>
       </c>
       <c r="B124" s="2">
-        <v>4.21767388877032</v>
+        <v>4.217673888770321</v>
       </c>
       <c r="C124" s="2">
         <v>126.7019815181847</v>
@@ -2913,7 +2913,7 @@
         <v>6</v>
       </c>
       <c r="E124" s="2">
-        <v>5.343876391047072</v>
+        <v>5.343876391047074</v>
       </c>
     </row>
     <row r="125" spans="1:5">
